--- a/ZonasEscolares/excels/LORETO-REQUENA-REQUENA.xlsx
+++ b/ZonasEscolares/excels/LORETO-REQUENA-REQUENA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1270,6 +1270,58 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>160501</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LORETO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>REQUENA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>REQUENA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>388058</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>60640</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>-5.0684</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-73.8539</v>
+      </c>
+      <c r="I17" t="n">
+        <v>172</v>
+      </c>
+      <c r="J17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ZonasEscolares/excels/LORETO-REQUENA-REQUENA.xlsx
+++ b/ZonasEscolares/excels/LORETO-REQUENA-REQUENA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LORETO-REQUENA-REQUENA.xlsx
+++ b/ZonasEscolares/excels/LORETO-REQUENA-REQUENA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,66 +413,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>438 DELIA ELIZABETH MARINHO VIENA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-5.0508</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-73.846</v>
-      </c>
-      <c r="I2" t="n">
-        <v>240</v>
-      </c>
-      <c r="J2" t="n">
-        <v>11</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-5.0508</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-73.846</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>PADRE NICOLAS GINER</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-5.070775</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-73.857201</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1071</v>
-      </c>
-      <c r="J3" t="n">
-        <v>54</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-5.070775</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-73.857201</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1071</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>60610</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-5.05761</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-73.852142</v>
-      </c>
-      <c r="I4" t="n">
-        <v>285</v>
-      </c>
-      <c r="J4" t="n">
-        <v>21</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-5.05761</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-73.852142</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>60644 VICTOR RAUL H. DE LA TORRE</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-5.0523</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-73.8475</v>
-      </c>
-      <c r="I5" t="n">
-        <v>494</v>
-      </c>
-      <c r="J5" t="n">
-        <v>26</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-5.0523</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-73.8475</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>60657 LIBERTADOR SIMON BOLIVAR</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-5.0425</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-73.8372</v>
-      </c>
-      <c r="I6" t="n">
-        <v>609</v>
-      </c>
-      <c r="J6" t="n">
-        <v>34</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-5.0425</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-73.8372</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>60789 SARGENTO II FERNANDO LORES</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-5.0613</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-73.85169999999999</v>
-      </c>
-      <c r="I7" t="n">
-        <v>218</v>
-      </c>
-      <c r="J7" t="n">
-        <v>12</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-5.0613</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-73.8517</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>61025 ISAURA CASIANA MAFALDO GORDON</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-5.066269</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-73.856629</v>
-      </c>
-      <c r="I8" t="n">
-        <v>903</v>
-      </c>
-      <c r="J8" t="n">
-        <v>51</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-5.066269</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-73.856629</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>PADRE AGUSTIN LOPEZ PARDO</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-5.063206</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-73.855283</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1229</v>
-      </c>
-      <c r="J9" t="n">
-        <v>58</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-5.063206</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-73.855283</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1229</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>MARIA INMACULADA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-5.063798</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-73.855717</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1026</v>
-      </c>
-      <c r="J10" t="n">
-        <v>56</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-5.063798</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-73.855717</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1026</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>FRAY FLORENCIO PASCUAL ALEGRE GONZALEZ</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-5.057964</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-73.85095800000001</v>
-      </c>
-      <c r="I11" t="n">
-        <v>677</v>
-      </c>
-      <c r="J11" t="n">
-        <v>32</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-5.057964</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-73.850958</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>60700 JUAN PABLO II</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-5.0558</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-73.8455</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1183</v>
-      </c>
-      <c r="J12" t="n">
-        <v>58</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-5.0558</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-73.8455</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1183</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>601542</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-5.0581</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-73.8507</v>
-      </c>
-      <c r="I13" t="n">
-        <v>344</v>
-      </c>
-      <c r="J13" t="n">
-        <v>20</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-5.0581</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-73.8507</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>SAN JUAN BAUTISTA LA SALLE</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-5.053342</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-73.84590300000001</v>
-      </c>
-      <c r="I14" t="n">
-        <v>444</v>
-      </c>
-      <c r="J14" t="n">
-        <v>32</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-5.053342</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-73.845903</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>718 SANTA CATALINA MARTIR</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-5.0668</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-73.8472</v>
-      </c>
-      <c r="I15" t="n">
-        <v>415</v>
-      </c>
-      <c r="J15" t="n">
-        <v>20</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-5.0668</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-73.8472</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>277 DIVINO NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-5.0649</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-73.8567</v>
-      </c>
-      <c r="I16" t="n">
-        <v>266</v>
-      </c>
-      <c r="J16" t="n">
-        <v>17</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-5.0649</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-73.8567</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,22 +1439,280 @@
           <t>60640</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-5.0684</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-73.8539</v>
-      </c>
-      <c r="I17" t="n">
-        <v>172</v>
-      </c>
-      <c r="J17" t="n">
-        <v>10</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-5.0684</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-73.8539</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>160501</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LORETO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>REQUENA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>REQUENA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>388020</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>60613 MANAOS</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-5.0601</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-73.8555</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>160501</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LORETO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>REQUENA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>REQUENA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>633187</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VILLA TUMBITO</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-5.07402516</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-73.85650227</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>160501</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LORETO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>REQUENA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>REQUENA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>753392</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>601568</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-5.07372912</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-73.85636315</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>160501</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LORETO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>REQUENA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>REQUENA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>753429</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>60651</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-5.06902654</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-73.84587085</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/ZonasEscolares/excels/LORETO-REQUENA-REQUENA.xlsx
+++ b/ZonasEscolares/excels/LORETO-REQUENA-REQUENA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>387822</t>
+          <t>388058</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>438 DELIA ELIZABETH MARINHO VIENA</t>
+          <t>60640</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-5.0508</t>
+          <t>-5.0684</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-73.846</t>
+          <t>-73.8539</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>172</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>387978</t>
+          <t>387822</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PADRE NICOLAS GINER</t>
+          <t>438 DELIA ELIZABETH MARINHO VIENA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-5.070775</t>
+          <t>-5.0508</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-73.857201</t>
+          <t>-73.846</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>240</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>388015</t>
+          <t>388237</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60610</t>
+          <t>60789 SARGENTO II FERNANDO LORES</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-5.05761</t>
+          <t>-5.0613</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-73.852142</t>
+          <t>-73.8517</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>218</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>388077</t>
+          <t>753434</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60644 VICTOR RAUL H. DE LA TORRE</t>
+          <t>277 DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-5.0523</t>
+          <t>-5.0649</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-73.8475</t>
+          <t>-73.8567</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>266</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>388162</t>
+          <t>388478</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60657 LIBERTADOR SIMON BOLIVAR</t>
+          <t>601542</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-5.0425</t>
+          <t>-5.0581</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-73.8372</t>
+          <t>-73.8507</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>344</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>388237</t>
+          <t>388609</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60789 SARGENTO II FERNANDO LORES</t>
+          <t>718 SANTA CATALINA MARTIR</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-5.0613</t>
+          <t>-5.0668</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-73.8517</t>
+          <t>-73.8472</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>415</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>388256</t>
+          <t>388015</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61025 ISAURA CASIANA MAFALDO GORDON</t>
+          <t>60610</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-5.066269</t>
+          <t>-5.05761</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-73.856629</t>
+          <t>-73.852142</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>285</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>388261</t>
+          <t>388077</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PADRE AGUSTIN LOPEZ PARDO</t>
+          <t>60644 VICTOR RAUL H. DE LA TORRE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5.063206</t>
+          <t>-5.0523</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-73.855283</t>
+          <t>-73.8475</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>494</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>388275</t>
+          <t>388384</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MARIA INMACULADA</t>
+          <t>FRAY FLORENCIO PASCUAL ALEGRE GONZALEZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-5.063798</t>
+          <t>-5.057964</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-73.855717</t>
+          <t>-73.850958</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>677</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,27 +1059,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>388384</t>
+          <t>388497</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FRAY FLORENCIO PASCUAL ALEGRE GONZALEZ</t>
+          <t>SAN JUAN BAUTISTA LA SALLE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-5.057964</t>
+          <t>-5.053342</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-73.850958</t>
+          <t>-73.845903</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>444</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>388440</t>
+          <t>388162</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60700 JUAN PABLO II</t>
+          <t>60657 LIBERTADOR SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-5.0558</t>
+          <t>-5.0425</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-73.8455</t>
+          <t>-73.8372</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>609</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>388478</t>
+          <t>388256</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>601542</t>
+          <t>61025 ISAURA CASIANA MAFALDO GORDON</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5.0581</t>
+          <t>-5.066269</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-73.8507</t>
+          <t>-73.856629</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>903</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>388497</t>
+          <t>387978</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SAN JUAN BAUTISTA LA SALLE</t>
+          <t>PADRE NICOLAS GINER</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-5.053342</t>
+          <t>-5.070775</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-73.845903</t>
+          <t>-73.857201</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>388609</t>
+          <t>388275</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>718 SANTA CATALINA MARTIR</t>
+          <t>MARIA INMACULADA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-5.0668</t>
+          <t>-5.063798</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-73.8472</t>
+          <t>-73.855717</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>753434</t>
+          <t>388261</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>277 DIVINO NIÑO JESUS</t>
+          <t>PADRE AGUSTIN LOPEZ PARDO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-5.0649</t>
+          <t>-5.063206</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-73.8567</t>
+          <t>-73.855283</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>388058</t>
+          <t>388440</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60640</t>
+          <t>60700 JUAN PABLO II</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.0684</t>
+          <t>-5.0558</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-73.8539</t>
+          <t>-73.8455</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">

--- a/ZonasEscolares/excels/LORETO-REQUENA-REQUENA.xlsx
+++ b/ZonasEscolares/excels/LORETO-REQUENA-REQUENA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>388058</t>
+          <t>753434</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60640</t>
+          <t>277 DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-5.0684</t>
+          <t>266</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-73.8539</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>-5.0649</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-73.8567</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>387822</t>
+          <t>753429</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>438 DELIA ELIZABETH MARINHO VIENA</t>
+          <t>60651</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-5.0508</t>
+          <t>165</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-73.846</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>-5.06902654</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-73.84587085</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>388237</t>
+          <t>753392</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60789 SARGENTO II FERNANDO LORES</t>
+          <t>601568</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-5.0613</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-73.8517</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>-5.07372912</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-73.85636315</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>753434</t>
+          <t>633187</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>277 DIVINO NIÑO JESUS</t>
+          <t>VILLA TUMBITO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-5.0649</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-73.8567</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>-5.07402516</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-73.85650227</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>388478</t>
+          <t>388609</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>601542</t>
+          <t>718 SANTA CATALINA MARTIR</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-5.0581</t>
+          <t>415</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-73.8507</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>-5.0668</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-73.8472</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>388609</t>
+          <t>388497</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>718 SANTA CATALINA MARTIR</t>
+          <t>SAN JUAN BAUTISTA LA SALLE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-5.0668</t>
+          <t>444</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-73.8472</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>-5.053342</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-73.845903</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>388015</t>
+          <t>388478</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60610</t>
+          <t>601542</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-5.05761</t>
+          <t>344</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-73.852142</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>-5.0581</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-73.8507</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>388077</t>
+          <t>388440</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60644 VICTOR RAUL H. DE LA TORRE</t>
+          <t>60700 JUAN PABLO II</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5.0523</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-73.8475</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>-5.0558</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-73.8455</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1007,22 +1007,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>-5.057964</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>-73.850958</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>388497</t>
+          <t>388275</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SAN JUAN BAUTISTA LA SALLE</t>
+          <t>MARIA INMACULADA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-5.053342</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-73.845903</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>-5.063798</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-73.855717</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>388162</t>
+          <t>388261</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60657 LIBERTADOR SIMON BOLIVAR</t>
+          <t>PADRE AGUSTIN LOPEZ PARDO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-5.0425</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-73.8372</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>-5.063206</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-73.855283</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>-5.066269</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>-73.856629</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>903</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>51</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>387978</t>
+          <t>388237</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PADRE NICOLAS GINER</t>
+          <t>60789 SARGENTO II FERNANDO LORES</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-5.070775</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-73.857201</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>-5.0613</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-73.8517</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>388275</t>
+          <t>388162</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MARIA INMACULADA</t>
+          <t>60657 LIBERTADOR SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-5.063798</t>
+          <t>609</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-73.855717</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>-5.0425</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-73.8372</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>388261</t>
+          <t>388077</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PADRE AGUSTIN LOPEZ PARDO</t>
+          <t>60644 VICTOR RAUL H. DE LA TORRE</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-5.063206</t>
+          <t>494</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-73.855283</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>-5.0523</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-73.8475</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>388440</t>
+          <t>388058</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60700 JUAN PABLO II</t>
+          <t>60640</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.0558</t>
+          <t>172</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-73.8455</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>-5.0684</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-73.8539</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1503,22 +1503,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>-5.0601</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>-73.8555</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>633187</t>
+          <t>388015</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VILLA TUMBITO</t>
+          <t>60610</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-5.07402516</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-73.85650227</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-5.05761</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-73.852142</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>753392</t>
+          <t>387978</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>601568</t>
+          <t>PADRE NICOLAS GINER</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-5.07372912</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-73.85636315</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-5.070775</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-73.857201</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>753429</t>
+          <t>387822</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60651</t>
+          <t>438 DELIA ELIZABETH MARINHO VIENA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-5.06902654</t>
+          <t>240</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-73.84587085</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>-5.0508</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-73.846</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">

--- a/ZonasEscolares/excels/LORETO-REQUENA-REQUENA.xlsx
+++ b/ZonasEscolares/excels/LORETO-REQUENA-REQUENA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
